--- a/Demo_Agent_Logins.xlsx
+++ b/Demo_Agent_Logins.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Active Hierarchy Logins" sheetId="1" r:id="rId1"/>
+    <sheet name="Active Demo Logins" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,505 +397,1259 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>Agent Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Agent Code</v>
+      </c>
+      <c r="C1" t="str">
         <v>Rank</v>
       </c>
-      <c r="B1" t="str">
-        <v>Agent Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Agent Code</v>
-      </c>
       <c r="D1" t="str">
+        <v>Sponsor Name</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Sponsor Code</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Branch</v>
+      </c>
+      <c r="G1" t="str">
         <v>Email</v>
       </c>
-      <c r="E1" t="str">
-        <v>Mobile</v>
-      </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>Password</v>
       </c>
-      <c r="G1" t="str">
-        <v>Sponsor</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Branch</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="str">
+        <v>Viraj Bhalekar</v>
+      </c>
+      <c r="B2" t="str">
+        <v>QA18</v>
+      </c>
+      <c r="C2">
         <v>18</v>
       </c>
-      <c r="B2" t="str">
+      <c r="D2" t="str">
+        <v>None</v>
+      </c>
+      <c r="E2" t="str">
+        <v>None</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G2" t="str">
+        <v>qa_rank18_60346@apex.test</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Rajesh Kulkarni</v>
+      </c>
+      <c r="B3" t="str">
+        <v>QA17</v>
+      </c>
+      <c r="C3">
+        <v>17</v>
+      </c>
+      <c r="D3" t="str">
         <v>Viraj Bhalekar</v>
       </c>
-      <c r="C2" t="str">
+      <c r="E3" t="str">
         <v>QA18</v>
       </c>
-      <c r="D2" t="str">
-        <v>qa_rank18_60346@apex.test</v>
-      </c>
-      <c r="E2" t="str">
-        <v>9055183115</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G2" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>17</v>
-      </c>
-      <c r="B3" t="str">
+      <c r="F3" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G3" t="str">
+        <v>qa_rank17_57538@apex.test</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Anjali Dubey</v>
+      </c>
+      <c r="B4" t="str">
+        <v>QA16</v>
+      </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
+      <c r="D4" t="str">
         <v>Rajesh Kulkarni</v>
       </c>
-      <c r="C3" t="str">
+      <c r="E4" t="str">
         <v>QA17</v>
       </c>
-      <c r="D3" t="str">
-        <v>qa_rank17_57538@apex.test</v>
-      </c>
-      <c r="E3" t="str">
-        <v>9062437316</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G3" t="str">
-        <v>QA18 - Viraj Bhalekar</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>16</v>
-      </c>
-      <c r="B4" t="str">
+      <c r="F4" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G4" t="str">
+        <v>qa_rank16_47420@apex.test</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Meera Rao</v>
+      </c>
+      <c r="B5" t="str">
+        <v>QA15</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
+      <c r="D5" t="str">
         <v>Anjali Dubey</v>
       </c>
-      <c r="C4" t="str">
+      <c r="E5" t="str">
         <v>QA16</v>
       </c>
-      <c r="D4" t="str">
-        <v>qa_rank16_47420@apex.test</v>
-      </c>
-      <c r="E4" t="str">
-        <v>9027103868</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G4" t="str">
-        <v>QA17 - Rajesh Kulkarni</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>15</v>
-      </c>
-      <c r="B5" t="str">
+      <c r="F5" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G5" t="str">
+        <v>qa_rank15_73338@apex.test</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Kiran Shah</v>
+      </c>
+      <c r="B6" t="str">
+        <v>QA14</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6" t="str">
         <v>Meera Rao</v>
       </c>
-      <c r="C5" t="str">
+      <c r="E6" t="str">
         <v>QA15</v>
       </c>
-      <c r="D5" t="str">
-        <v>qa_rank15_73338@apex.test</v>
-      </c>
-      <c r="E5" t="str">
-        <v>9084714747</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G5" t="str">
-        <v>QA16 - Anjali Dubey</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>14</v>
-      </c>
-      <c r="B6" t="str">
+      <c r="F6" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G6" t="str">
+        <v>qa_rank14_48946@apex.test</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Deepa Menon</v>
+      </c>
+      <c r="B7" t="str">
+        <v>QA13</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7" t="str">
         <v>Kiran Shah</v>
       </c>
-      <c r="C6" t="str">
+      <c r="E7" t="str">
         <v>QA14</v>
       </c>
-      <c r="D6" t="str">
-        <v>qa_rank14_48946@apex.test</v>
-      </c>
-      <c r="E6" t="str">
-        <v>9072203037</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G6" t="str">
-        <v>QA15 - Meera Rao</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>13</v>
-      </c>
-      <c r="B7" t="str">
+      <c r="F7" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G7" t="str">
+        <v>qa_rank13_93180@apex.test</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Ravi Verma</v>
+      </c>
+      <c r="B8" t="str">
+        <v>QA12</v>
+      </c>
+      <c r="C8">
+        <v>12</v>
+      </c>
+      <c r="D8" t="str">
         <v>Deepa Menon</v>
       </c>
-      <c r="C7" t="str">
+      <c r="E8" t="str">
         <v>QA13</v>
       </c>
-      <c r="D7" t="str">
-        <v>qa_rank13_93180@apex.test</v>
-      </c>
-      <c r="E7" t="str">
-        <v>9080423237</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G7" t="str">
-        <v>QA14 - Kiran Shah</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>12</v>
-      </c>
-      <c r="B8" t="str">
+      <c r="F8" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G8" t="str">
+        <v>qa_rank12_84776@apex.test</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Pooja Nair</v>
+      </c>
+      <c r="B9" t="str">
+        <v>QA11</v>
+      </c>
+      <c r="C9">
+        <v>11</v>
+      </c>
+      <c r="D9" t="str">
         <v>Ravi Verma</v>
       </c>
-      <c r="C8" t="str">
+      <c r="E9" t="str">
         <v>QA12</v>
       </c>
-      <c r="D8" t="str">
-        <v>qa_rank12_84776@apex.test</v>
-      </c>
-      <c r="E8" t="str">
-        <v>9086182743</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G8" t="str">
-        <v>QA13 - Deepa Menon</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>11</v>
-      </c>
-      <c r="B9" t="str">
+      <c r="F9" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G9" t="str">
+        <v>qa_rank11_42618@apex.test</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Suresh Kumar</v>
+      </c>
+      <c r="B10" t="str">
+        <v>QA10</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10" t="str">
         <v>Pooja Nair</v>
       </c>
-      <c r="C9" t="str">
+      <c r="E10" t="str">
         <v>QA11</v>
       </c>
-      <c r="D9" t="str">
-        <v>qa_rank11_42618@apex.test</v>
-      </c>
-      <c r="E9" t="str">
-        <v>9023790382</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G9" t="str">
-        <v>QA12 - Ravi Verma</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>10</v>
-      </c>
-      <c r="B10" t="str">
+      <c r="F10" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G10" t="str">
+        <v>qa_rank10_98220@apex.test</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Kavita Reddy</v>
+      </c>
+      <c r="B11" t="str">
+        <v>QA09</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11" t="str">
         <v>Suresh Kumar</v>
       </c>
-      <c r="C10" t="str">
+      <c r="E11" t="str">
         <v>QA10</v>
       </c>
-      <c r="D10" t="str">
-        <v>qa_rank10_98220@apex.test</v>
-      </c>
-      <c r="E10" t="str">
-        <v>9014110072</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G10" t="str">
-        <v>QA11 - Pooja Nair</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="str">
+      <c r="F11" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G11" t="str">
+        <v>qa_rank9_73010@apex.test</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Anand Joshi</v>
+      </c>
+      <c r="B12" t="str">
+        <v>QA08</v>
+      </c>
+      <c r="C12">
+        <v>8</v>
+      </c>
+      <c r="D12" t="str">
         <v>Kavita Reddy</v>
       </c>
-      <c r="C11" t="str">
+      <c r="E12" t="str">
         <v>QA09</v>
       </c>
-      <c r="D11" t="str">
-        <v>qa_rank9_73010@apex.test</v>
-      </c>
-      <c r="E11" t="str">
-        <v>9087151844</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G11" t="str">
-        <v>QA10 - Suresh Kumar</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>8</v>
-      </c>
-      <c r="B12" t="str">
+      <c r="F12" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G12" t="str">
+        <v>qa_rank8_11457@apex.test</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Vikram Singh</v>
+      </c>
+      <c r="B13" t="str">
+        <v>QA07</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13" t="str">
         <v>Anand Joshi</v>
       </c>
-      <c r="C12" t="str">
+      <c r="E13" t="str">
         <v>QA08</v>
       </c>
-      <c r="D12" t="str">
-        <v>qa_rank8_11457@apex.test</v>
-      </c>
-      <c r="E12" t="str">
-        <v>9064174680</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G12" t="str">
-        <v>QA09 - Kavita Reddy</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>7</v>
-      </c>
-      <c r="B13" t="str">
+      <c r="F13" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G13" t="str">
+        <v>qa_rank7_22344@apex.test</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Sneha Iyer</v>
+      </c>
+      <c r="B14" t="str">
+        <v>QA06</v>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14" t="str">
         <v>Vikram Singh</v>
       </c>
-      <c r="C13" t="str">
+      <c r="E14" t="str">
         <v>QA07</v>
       </c>
-      <c r="D13" t="str">
-        <v>qa_rank7_22344@apex.test</v>
-      </c>
-      <c r="E13" t="str">
-        <v>9019128513</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G13" t="str">
-        <v>QA08 - Anand Joshi</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>6</v>
-      </c>
-      <c r="B14" t="str">
+      <c r="F14" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G14" t="str">
+        <v>qa_rank6_26634@apex.test</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Rohit Chawla</v>
+      </c>
+      <c r="B15" t="str">
+        <v>QA05</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15" t="str">
         <v>Sneha Iyer</v>
       </c>
-      <c r="C14" t="str">
+      <c r="E15" t="str">
         <v>QA06</v>
       </c>
-      <c r="D14" t="str">
-        <v>qa_rank6_26634@apex.test</v>
-      </c>
-      <c r="E14" t="str">
-        <v>9025934010</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G14" t="str">
-        <v>QA07 - Vikram Singh</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15" t="str">
+      <c r="F15" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G15" t="str">
+        <v>qa_rank5_50018@apex.test</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Priya Desai</v>
+      </c>
+      <c r="B16" t="str">
+        <v>QA04</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16" t="str">
         <v>Rohit Chawla</v>
       </c>
-      <c r="C15" t="str">
+      <c r="E16" t="str">
         <v>QA05</v>
       </c>
-      <c r="D15" t="str">
-        <v>qa_rank5_50018@apex.test</v>
-      </c>
-      <c r="E15" t="str">
-        <v>9044556237</v>
-      </c>
-      <c r="F15" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G15" t="str">
-        <v>QA06 - Sneha Iyer</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>4</v>
-      </c>
-      <c r="B16" t="str">
+      <c r="F16" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G16" t="str">
+        <v>qa_rank4_18956@apex.test</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Kavita Reddy (Mgr)</v>
+      </c>
+      <c r="B17" t="str">
+        <v>AG001024</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17" t="str">
         <v>Priya Desai</v>
       </c>
-      <c r="C16" t="str">
+      <c r="E17" t="str">
         <v>QA04</v>
       </c>
-      <c r="D16" t="str">
-        <v>qa_rank4_18956@apex.test</v>
-      </c>
-      <c r="E16" t="str">
-        <v>9024549230</v>
-      </c>
-      <c r="F16" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G16" t="str">
-        <v>QA05 - Rohit Chawla</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
+      <c r="F17" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G17" t="str">
+        <v>agentag1000_36339@apex.test</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Sanjay Mishra</v>
+      </c>
+      <c r="B18" t="str">
+        <v>QA03</v>
+      </c>
+      <c r="C18">
         <v>3</v>
       </c>
-      <c r="B17" t="str">
+      <c r="D18" t="str">
+        <v>Priya Desai</v>
+      </c>
+      <c r="E18" t="str">
+        <v>QA04</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G18" t="str">
+        <v>qa_rank3_83768@apex.test</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Vikram Malhotra</v>
+      </c>
+      <c r="B19" t="str">
+        <v>KB001043</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19" t="str">
         <v>Sanjay Mishra</v>
       </c>
-      <c r="C17" t="str">
+      <c r="E19" t="str">
         <v>QA03</v>
       </c>
-      <c r="D17" t="str">
-        <v>qa_rank3_83768@apex.test</v>
-      </c>
-      <c r="E17" t="str">
-        <v>9017289602</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G17" t="str">
-        <v>QA04 - Priya Desai</v>
-      </c>
-      <c r="H17" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
+      <c r="F19" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G19" t="str">
+        <v>agentkb001043_4119@apex.com</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Rahul Sharma</v>
+      </c>
+      <c r="B20" t="str">
+        <v>AG1002</v>
+      </c>
+      <c r="C20">
         <v>2</v>
       </c>
-      <c r="B18" t="str">
+      <c r="D20" t="str">
+        <v>Kavita Reddy (Mgr)</v>
+      </c>
+      <c r="E20" t="str">
+        <v>AG001024</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G20" t="str">
+        <v>agentag1002_71616@apex.test</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Rohit Chawla</v>
+      </c>
+      <c r="B21" t="str">
+        <v>AG1001</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Kavita Reddy (Mgr)</v>
+      </c>
+      <c r="E21" t="str">
+        <v>AG001024</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G21" t="str">
+        <v>agentag1001_45738@apex.test</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Amit Patel</v>
+      </c>
+      <c r="B22" t="str">
+        <v>AG1003</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Kavita Reddy (Mgr)</v>
+      </c>
+      <c r="E22" t="str">
+        <v>AG001024</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G22" t="str">
+        <v>agentag1003_6912@apex.test</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Rohit Chawla</v>
+      </c>
+      <c r="B23" t="str">
+        <v>AG001023</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Kavita Reddy (Mgr)</v>
+      </c>
+      <c r="E23" t="str">
+        <v>AG001024</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G23" t="str">
+        <v>agentag1002_72346@apex.test</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
         <v>Neha Gupta</v>
       </c>
-      <c r="C18" t="str">
+      <c r="B24" t="str">
         <v>QA02</v>
       </c>
-      <c r="D18" t="str">
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Sanjay Mishra</v>
+      </c>
+      <c r="E24" t="str">
+        <v>QA03</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G24" t="str">
         <v>qa_rank2_24399@apex.test</v>
       </c>
-      <c r="E18" t="str">
-        <v>9069512788</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G18" t="str">
-        <v>QA03 - Sanjay Mishra</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Mumbai Central</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>1</v>
-      </c>
-      <c r="B19" t="str">
+      <c r="H24" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Gaurav Jain</v>
+      </c>
+      <c r="B25" t="str">
+        <v>AG001030</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Kavita Reddy (Mgr)</v>
+      </c>
+      <c r="E25" t="str">
+        <v>AG001024</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G25" t="str">
+        <v>agentag1001_47011@apex.test</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
         <v>Amit Patel</v>
       </c>
-      <c r="C19" t="str">
+      <c r="B26" t="str">
+        <v>AG1004</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Kavita Reddy (Mgr)</v>
+      </c>
+      <c r="E26" t="str">
+        <v>AG001024</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G26" t="str">
+        <v>agentag1004_26533@apex.test</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Gaurav Jain</v>
+      </c>
+      <c r="B27" t="str">
+        <v>AG001031</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Kavita Reddy (Mgr)</v>
+      </c>
+      <c r="E27" t="str">
+        <v>AG001024</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G27" t="str">
+        <v>agentag1004_65095@apex.test</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Shruti Bansal</v>
+      </c>
+      <c r="B28" t="str">
+        <v>AG001039</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Kavita Reddy (Mgr)</v>
+      </c>
+      <c r="E28" t="str">
+        <v>AG001024</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G28" t="str">
+        <v>agentag1003_3686@apex.test</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Alok Pandey</v>
+      </c>
+      <c r="B29" t="str">
+        <v>AG1008</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Gaurav Jain</v>
+      </c>
+      <c r="E29" t="str">
+        <v>AG001030</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G29" t="str">
+        <v>agentag1008_17506@apex.test</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Rahul Sharma</v>
+      </c>
+      <c r="B30" t="str">
+        <v>AG1015</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Shruti Bansal</v>
+      </c>
+      <c r="E30" t="str">
+        <v>AG001039</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G30" t="str">
+        <v>agentag1015_16691@apex.test</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Priya Desai</v>
+      </c>
+      <c r="B31" t="str">
+        <v>AG1007</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Gaurav Jain</v>
+      </c>
+      <c r="E31" t="str">
+        <v>AG001031</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G31" t="str">
+        <v>agentag1007_67398@apex.test</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Shruti Bansal</v>
+      </c>
+      <c r="B32" t="str">
+        <v>AG1010</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Shruti Bansal</v>
+      </c>
+      <c r="E32" t="str">
+        <v>AG001039</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G32" t="str">
+        <v>agentag1010_92687@apex.test</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Meera Rao</v>
+      </c>
+      <c r="B33" t="str">
+        <v>AG1011</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Gaurav Jain</v>
+      </c>
+      <c r="E33" t="str">
+        <v>AG001030</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G33" t="str">
+        <v>agentag1011_72217@apex.test</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Swati Bhat</v>
+      </c>
+      <c r="B34" t="str">
+        <v>AG1014</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Shruti Bansal</v>
+      </c>
+      <c r="E34" t="str">
+        <v>AG001039</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G34" t="str">
+        <v>agentag1014_31312@apex.test</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Anand Joshi</v>
+      </c>
+      <c r="B35" t="str">
+        <v>AG001021</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Shruti Bansal</v>
+      </c>
+      <c r="E35" t="str">
+        <v>AG001039</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G35" t="str">
+        <v>agentag1010_12791@apex.test</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Ravi Verma</v>
+      </c>
+      <c r="B36" t="str">
+        <v>AG1012</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Gaurav Jain</v>
+      </c>
+      <c r="E36" t="str">
+        <v>AG001031</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G36" t="str">
+        <v>agentag1012_72182@apex.test</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Shruti Bansal</v>
+      </c>
+      <c r="B37" t="str">
+        <v>AG1009</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Gaurav Jain</v>
+      </c>
+      <c r="E37" t="str">
+        <v>AG001031</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G37" t="str">
+        <v>agentag1009_55156@apex.test</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Sanjay Mishra</v>
+      </c>
+      <c r="B38" t="str">
+        <v>AG1016</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Gaurav Jain</v>
+      </c>
+      <c r="E38" t="str">
+        <v>AG001031</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G38" t="str">
+        <v>agentag1016_18117@apex.test</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Neha Gupta</v>
+      </c>
+      <c r="B39" t="str">
+        <v>AG1006</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Gaurav Jain</v>
+      </c>
+      <c r="E39" t="str">
+        <v>AG001030</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G39" t="str">
+        <v>agentag1006_18578@apex.test</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Meera Rao</v>
+      </c>
+      <c r="B40" t="str">
+        <v>AG001022</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Gaurav Jain</v>
+      </c>
+      <c r="E40" t="str">
+        <v>AG001031</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G40" t="str">
+        <v>agentag1009_69309@apex.test</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Alok Pandey</v>
+      </c>
+      <c r="B41" t="str">
+        <v>AG001025</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Shruti Bansal</v>
+      </c>
+      <c r="E41" t="str">
+        <v>AG001039</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G41" t="str">
+        <v>agentag1016_31621@apex.test</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Nisha Bajaj</v>
+      </c>
+      <c r="B42" t="str">
+        <v>AG1018</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Rohit Chawla</v>
+      </c>
+      <c r="E42" t="str">
+        <v>AG001023</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G42" t="str">
+        <v>agentag1018_38598@apex.test</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Rohit Chawla</v>
+      </c>
+      <c r="B43" t="str">
+        <v>AG001026</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Gaurav Jain</v>
+      </c>
+      <c r="E43" t="str">
+        <v>AG001030</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G43" t="str">
+        <v>agentag1012_53265@apex.test</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Sneha Iyer</v>
+      </c>
+      <c r="B44" t="str">
+        <v>AG001027</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Gaurav Jain</v>
+      </c>
+      <c r="E44" t="str">
+        <v>AG001031</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G44" t="str">
+        <v>agentag1008_27267@apex.test</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Nisha Bajaj</v>
+      </c>
+      <c r="B45" t="str">
+        <v>AG1019</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Shruti Bansal</v>
+      </c>
+      <c r="E45" t="str">
+        <v>AG001039</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G45" t="str">
+        <v>agentag1019_33011@apex.test</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Alok Pandey</v>
+      </c>
+      <c r="B46" t="str">
+        <v>AG001028</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Gaurav Jain</v>
+      </c>
+      <c r="E46" t="str">
+        <v>AG001031</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G46" t="str">
+        <v>agentag1006_13280@apex.test</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Anand Joshi</v>
+      </c>
+      <c r="B47" t="str">
+        <v>AG001029</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Gaurav Jain</v>
+      </c>
+      <c r="E47" t="str">
+        <v>AG001030</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G47" t="str">
+        <v>agentag1018_6055@apex.test</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Demo@123</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Amit Patel</v>
+      </c>
+      <c r="B48" t="str">
         <v>QA01</v>
       </c>
-      <c r="D19" t="str">
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Neha Gupta</v>
+      </c>
+      <c r="E48" t="str">
+        <v>QA02</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Mumbai Central</v>
+      </c>
+      <c r="G48" t="str">
         <v>qa_rank1_56610@apex.test</v>
       </c>
-      <c r="E19" t="str">
-        <v>9042078363</v>
-      </c>
-      <c r="F19" t="str">
-        <v>Demo@123</v>
-      </c>
-      <c r="G19" t="str">
-        <v>QA02 - Neha Gupta</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Mumbai Central</v>
+      <c r="H48" t="str">
+        <v>Demo@123</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H48"/>
   </ignoredErrors>
 </worksheet>
 </file>